--- a/public/TagLBMT.xlsx
+++ b/public/TagLBMT.xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24131"/>
-  <workbookPr defaultThemeVersion="166925"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HPDQ-SAM\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\truonghoaisam\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6933BCC3-07A1-4D5E-9FF2-4D3A914585CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="1" activeTab="2" xr2:uid="{BFBE29CB-D38E-42E2-A34C-B8631848C5A2}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="1" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="LBMTDuoiMay" sheetId="5" r:id="rId1"/>
@@ -18,7 +17,7 @@
     <sheet name="LBMT_MQ" sheetId="8" r:id="rId3"/>
     <sheet name="Tram Lam Mat" sheetId="24" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -28,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="402" uniqueCount="200">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="402" uniqueCount="199">
   <si>
     <t>Góc mở cửa gió</t>
   </si>
@@ -217,9 +216,6 @@
   </si>
   <si>
     <t>Khu vực: Máng quặng #2</t>
-  </si>
-  <si>
-    <t>Chuyên áp</t>
   </si>
   <si>
     <t>Khu vực: Đuôi máy #2</t>
@@ -633,7 +629,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -824,7 +820,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="42">
+  <cellXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -852,67 +848,73 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -921,10 +923,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -933,12 +932,10 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1252,9 +1249,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{56FB44C8-E269-47C7-A268-20B56F5545AE}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:F36"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="22.28515625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="12.28515625" bestFit="1" customWidth="1"/>
@@ -1268,16 +1265,16 @@
       <c r="A1" s="10" t="s">
         <v>29</v>
       </c>
-      <c r="B1" s="18" t="s">
+      <c r="B1" s="13" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="19"/>
-      <c r="D1" s="20"/>
+      <c r="C1" s="14"/>
+      <c r="D1" s="15"/>
       <c r="E1" s="1" t="s">
         <v>1</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="17.25" x14ac:dyDescent="0.3">
@@ -1285,21 +1282,21 @@
       <c r="B2" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="C2" s="15" t="s">
+      <c r="C2" s="16" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="16"/>
+      <c r="D2" s="17"/>
       <c r="E2" s="1" t="s">
         <v>2</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="11"/>
       <c r="B3" s="11"/>
-      <c r="C3" s="31" t="s">
+      <c r="C3" s="18" t="s">
         <v>5</v>
       </c>
       <c r="D3" s="2" t="s">
@@ -1309,13 +1306,13 @@
         <v>4</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="11"/>
       <c r="B4" s="11"/>
-      <c r="C4" s="32"/>
+      <c r="C4" s="19"/>
       <c r="D4" s="2" t="s">
         <v>59</v>
       </c>
@@ -1323,13 +1320,13 @@
         <v>6</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A5" s="11"/>
       <c r="B5" s="11"/>
-      <c r="C5" s="33"/>
+      <c r="C5" s="20"/>
       <c r="D5" s="3" t="s">
         <v>60</v>
       </c>
@@ -1337,7 +1334,7 @@
         <v>9</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="17.25" x14ac:dyDescent="0.3">
@@ -1353,10 +1350,10 @@
         <v>11</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" s="11"/>
       <c r="B7" s="11"/>
       <c r="C7" s="22"/>
@@ -1367,10 +1364,10 @@
         <v>12</v>
       </c>
       <c r="F7" s="6" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" s="11"/>
       <c r="B8" s="11"/>
       <c r="C8" s="21" t="s">
@@ -1383,10 +1380,10 @@
         <v>13</v>
       </c>
       <c r="F8" s="6" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9" s="11"/>
       <c r="B9" s="12"/>
       <c r="C9" s="22"/>
@@ -1397,45 +1394,45 @@
         <v>16</v>
       </c>
       <c r="F9" s="6" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A10" s="11"/>
-      <c r="B10" s="17" t="s">
+      <c r="B10" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="C10" s="23" t="s">
+      <c r="C10" s="24" t="s">
         <v>15</v>
       </c>
-      <c r="D10" s="24"/>
+      <c r="D10" s="25"/>
       <c r="E10" s="1" t="s">
         <v>18</v>
       </c>
       <c r="F10" s="6" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" s="11"/>
-      <c r="B11" s="17"/>
-      <c r="C11" s="15" t="s">
+      <c r="B11" s="23"/>
+      <c r="C11" s="16" t="s">
         <v>17</v>
       </c>
-      <c r="D11" s="16"/>
+      <c r="D11" s="17"/>
       <c r="E11" s="1" t="s">
         <v>19</v>
       </c>
       <c r="F11" s="6" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" s="11"/>
       <c r="B12" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="C12" s="25" t="s">
+      <c r="C12" s="26" t="s">
         <v>31</v>
       </c>
       <c r="D12" s="1" t="s">
@@ -1445,13 +1442,13 @@
         <v>21</v>
       </c>
       <c r="F12" s="6" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13" s="11"/>
       <c r="B13" s="11"/>
-      <c r="C13" s="26"/>
+      <c r="C13" s="27"/>
       <c r="D13" s="1" t="s">
         <v>53</v>
       </c>
@@ -1459,13 +1456,13 @@
         <v>22</v>
       </c>
       <c r="F13" s="6" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14" s="11"/>
       <c r="B14" s="11"/>
-      <c r="C14" s="26"/>
+      <c r="C14" s="27"/>
       <c r="D14" s="1" t="s">
         <v>55</v>
       </c>
@@ -1473,13 +1470,13 @@
         <v>23</v>
       </c>
       <c r="F14" s="6" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A15" s="11"/>
       <c r="B15" s="12"/>
-      <c r="C15" s="27"/>
+      <c r="C15" s="28"/>
       <c r="D15" s="1" t="s">
         <v>56</v>
       </c>
@@ -1487,89 +1484,89 @@
         <v>24</v>
       </c>
       <c r="F15" s="6" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A16" s="11"/>
-      <c r="B16" s="28" t="s">
+      <c r="B16" s="29" t="s">
         <v>26</v>
       </c>
-      <c r="C16" s="29"/>
-      <c r="D16" s="30"/>
+      <c r="C16" s="30"/>
+      <c r="D16" s="31"/>
       <c r="E16" s="1" t="s">
         <v>25</v>
       </c>
       <c r="F16" s="6" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A17" s="11"/>
-      <c r="B17" s="13" t="s">
+      <c r="B17" s="32" t="s">
         <v>38</v>
       </c>
-      <c r="C17" s="15" t="s">
+      <c r="C17" s="16" t="s">
         <v>39</v>
       </c>
-      <c r="D17" s="16"/>
+      <c r="D17" s="17"/>
       <c r="E17" s="1" t="s">
         <v>27</v>
       </c>
       <c r="F17" s="6" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A18" s="12"/>
-      <c r="B18" s="14"/>
-      <c r="C18" s="15" t="s">
+      <c r="B18" s="33"/>
+      <c r="C18" s="16" t="s">
         <v>40</v>
       </c>
-      <c r="D18" s="16"/>
+      <c r="D18" s="17"/>
       <c r="E18" s="1" t="s">
         <v>28</v>
       </c>
       <c r="F18" s="6" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A19" s="10" t="s">
         <v>57</v>
       </c>
-      <c r="B19" s="18" t="s">
+      <c r="B19" s="13" t="s">
         <v>0</v>
       </c>
-      <c r="C19" s="19"/>
-      <c r="D19" s="20"/>
+      <c r="C19" s="14"/>
+      <c r="D19" s="15"/>
       <c r="E19" s="1" t="s">
         <v>32</v>
       </c>
       <c r="F19" s="6" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A20" s="11"/>
       <c r="B20" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="C20" s="15" t="s">
+      <c r="C20" s="16" t="s">
         <v>3</v>
       </c>
-      <c r="D20" s="16"/>
+      <c r="D20" s="17"/>
       <c r="E20" s="1" t="s">
         <v>33</v>
       </c>
       <c r="F20" s="6" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A21" s="11"/>
       <c r="B21" s="11"/>
-      <c r="C21" s="31" t="s">
+      <c r="C21" s="18" t="s">
         <v>5</v>
       </c>
       <c r="D21" s="2" t="s">
@@ -1579,13 +1576,13 @@
         <v>34</v>
       </c>
       <c r="F21" s="6" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A22" s="11"/>
       <c r="B22" s="11"/>
-      <c r="C22" s="32"/>
+      <c r="C22" s="19"/>
       <c r="D22" s="2" t="s">
         <v>59</v>
       </c>
@@ -1593,13 +1590,13 @@
         <v>35</v>
       </c>
       <c r="F22" s="6" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A23" s="11"/>
       <c r="B23" s="11"/>
-      <c r="C23" s="33"/>
+      <c r="C23" s="20"/>
       <c r="D23" s="3" t="s">
         <v>60</v>
       </c>
@@ -1607,10 +1604,10 @@
         <v>36</v>
       </c>
       <c r="F23" s="6" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A24" s="11"/>
       <c r="B24" s="11"/>
       <c r="C24" s="21" t="s">
@@ -1623,10 +1620,10 @@
         <v>37</v>
       </c>
       <c r="F24" s="6" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A25" s="11"/>
       <c r="B25" s="11"/>
       <c r="C25" s="22"/>
@@ -1637,10 +1634,10 @@
         <v>41</v>
       </c>
       <c r="F25" s="6" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A26" s="11"/>
       <c r="B26" s="11"/>
       <c r="C26" s="21" t="s">
@@ -1653,10 +1650,10 @@
         <v>42</v>
       </c>
       <c r="F26" s="6" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A27" s="11"/>
       <c r="B27" s="12"/>
       <c r="C27" s="22"/>
@@ -1667,45 +1664,45 @@
         <v>43</v>
       </c>
       <c r="F27" s="6" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A28" s="11"/>
-      <c r="B28" s="17" t="s">
+      <c r="B28" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="C28" s="23" t="s">
+      <c r="C28" s="24" t="s">
         <v>15</v>
       </c>
-      <c r="D28" s="24"/>
+      <c r="D28" s="25"/>
       <c r="E28" s="1" t="s">
         <v>44</v>
       </c>
       <c r="F28" s="6" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A29" s="11"/>
-      <c r="B29" s="17"/>
-      <c r="C29" s="15" t="s">
+      <c r="B29" s="23"/>
+      <c r="C29" s="16" t="s">
         <v>17</v>
       </c>
-      <c r="D29" s="16"/>
+      <c r="D29" s="17"/>
       <c r="E29" s="1" t="s">
         <v>45</v>
       </c>
       <c r="F29" s="6" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A30" s="11"/>
       <c r="B30" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="C30" s="25" t="s">
+      <c r="C30" s="26" t="s">
         <v>31</v>
       </c>
       <c r="D30" s="1" t="s">
@@ -1715,13 +1712,13 @@
         <v>46</v>
       </c>
       <c r="F30" s="6" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A31" s="11"/>
       <c r="B31" s="11"/>
-      <c r="C31" s="26"/>
+      <c r="C31" s="27"/>
       <c r="D31" s="1" t="s">
         <v>53</v>
       </c>
@@ -1729,13 +1726,13 @@
         <v>47</v>
       </c>
       <c r="F31" s="6" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A32" s="11"/>
       <c r="B32" s="11"/>
-      <c r="C32" s="26"/>
+      <c r="C32" s="27"/>
       <c r="D32" s="1" t="s">
         <v>55</v>
       </c>
@@ -1743,13 +1740,13 @@
         <v>48</v>
       </c>
       <c r="F32" s="6" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A33" s="11"/>
       <c r="B33" s="12"/>
-      <c r="C33" s="27"/>
+      <c r="C33" s="28"/>
       <c r="D33" s="1" t="s">
         <v>56</v>
       </c>
@@ -1757,55 +1754,71 @@
         <v>49</v>
       </c>
       <c r="F33" s="6" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A34" s="11"/>
-      <c r="B34" s="28" t="s">
+      <c r="B34" s="29" t="s">
         <v>26</v>
       </c>
-      <c r="C34" s="29"/>
-      <c r="D34" s="30"/>
+      <c r="C34" s="30"/>
+      <c r="D34" s="31"/>
       <c r="E34" s="1" t="s">
         <v>50</v>
       </c>
       <c r="F34" s="6" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A35" s="11"/>
-      <c r="B35" s="13" t="s">
+      <c r="B35" s="32" t="s">
         <v>38</v>
       </c>
-      <c r="C35" s="15" t="s">
+      <c r="C35" s="16" t="s">
         <v>39</v>
       </c>
-      <c r="D35" s="16"/>
+      <c r="D35" s="17"/>
       <c r="E35" s="1" t="s">
         <v>51</v>
       </c>
       <c r="F35" s="6" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A36" s="12"/>
-      <c r="B36" s="14"/>
-      <c r="C36" s="15" t="s">
+      <c r="B36" s="33"/>
+      <c r="C36" s="16" t="s">
         <v>40</v>
       </c>
-      <c r="D36" s="16"/>
+      <c r="D36" s="17"/>
       <c r="E36" s="1" t="s">
         <v>52</v>
       </c>
       <c r="F36" s="6" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="32">
+    <mergeCell ref="A1:A18"/>
+    <mergeCell ref="B17:B18"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="B10:B11"/>
+    <mergeCell ref="B1:D1"/>
+    <mergeCell ref="B2:B9"/>
+    <mergeCell ref="C8:C9"/>
+    <mergeCell ref="C6:C7"/>
+    <mergeCell ref="C2:D2"/>
+    <mergeCell ref="C10:D10"/>
+    <mergeCell ref="C12:C15"/>
+    <mergeCell ref="B12:B15"/>
+    <mergeCell ref="B16:D16"/>
+    <mergeCell ref="C3:C5"/>
+    <mergeCell ref="C11:D11"/>
     <mergeCell ref="A19:A36"/>
     <mergeCell ref="B19:D19"/>
     <mergeCell ref="B20:B27"/>
@@ -1822,22 +1835,6 @@
     <mergeCell ref="B35:B36"/>
     <mergeCell ref="C35:D35"/>
     <mergeCell ref="C36:D36"/>
-    <mergeCell ref="A1:A18"/>
-    <mergeCell ref="B17:B18"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="B10:B11"/>
-    <mergeCell ref="B1:D1"/>
-    <mergeCell ref="B2:B9"/>
-    <mergeCell ref="C8:C9"/>
-    <mergeCell ref="C6:C7"/>
-    <mergeCell ref="C2:D2"/>
-    <mergeCell ref="C10:D10"/>
-    <mergeCell ref="C12:C15"/>
-    <mergeCell ref="B12:B15"/>
-    <mergeCell ref="B16:D16"/>
-    <mergeCell ref="C3:C5"/>
-    <mergeCell ref="C11:D11"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1845,11 +1842,11 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2F5AC54A-498E-4EE9-BA49-9A4EB3FBFC04}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:F36"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="18.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="21.85546875" customWidth="1"/>
     <col min="2" max="2" width="12.28515625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="14.28515625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="7.85546875" bestFit="1" customWidth="1"/>
@@ -1857,42 +1854,42 @@
     <col min="6" max="6" width="20.42578125" style="7" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" s="10" t="s">
-        <v>64</v>
-      </c>
-      <c r="B1" s="18" t="s">
+        <v>63</v>
+      </c>
+      <c r="B1" s="13" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="19"/>
-      <c r="D1" s="20"/>
+      <c r="C1" s="14"/>
+      <c r="D1" s="15"/>
       <c r="E1" s="1" t="s">
         <v>1</v>
       </c>
       <c r="F1" s="6" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" s="11"/>
       <c r="B2" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="C2" s="15" t="s">
+      <c r="C2" s="16" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="16"/>
+      <c r="D2" s="17"/>
       <c r="E2" s="1" t="s">
         <v>2</v>
       </c>
       <c r="F2" s="6" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" s="11"/>
       <c r="B3" s="11"/>
-      <c r="C3" s="31" t="s">
+      <c r="C3" s="18" t="s">
         <v>5</v>
       </c>
       <c r="D3" s="2" t="s">
@@ -1902,13 +1899,13 @@
         <v>4</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" s="11"/>
       <c r="B4" s="11"/>
-      <c r="C4" s="32"/>
+      <c r="C4" s="19"/>
       <c r="D4" s="2" t="s">
         <v>59</v>
       </c>
@@ -1916,13 +1913,13 @@
         <v>6</v>
       </c>
       <c r="F4" s="6" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A5" s="11"/>
       <c r="B5" s="11"/>
-      <c r="C5" s="33"/>
+      <c r="C5" s="20"/>
       <c r="D5" s="3" t="s">
         <v>60</v>
       </c>
@@ -1930,10 +1927,10 @@
         <v>9</v>
       </c>
       <c r="F5" s="6" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" s="11"/>
       <c r="B6" s="11"/>
       <c r="C6" s="21" t="s">
@@ -1946,10 +1943,10 @@
         <v>11</v>
       </c>
       <c r="F6" s="6" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" s="11"/>
       <c r="B7" s="11"/>
       <c r="C7" s="22"/>
@@ -1960,10 +1957,10 @@
         <v>12</v>
       </c>
       <c r="F7" s="6" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" s="11"/>
       <c r="B8" s="11"/>
       <c r="C8" s="21" t="s">
@@ -1976,10 +1973,10 @@
         <v>13</v>
       </c>
       <c r="F8" s="6" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9" s="11"/>
       <c r="B9" s="12"/>
       <c r="C9" s="22"/>
@@ -1990,179 +1987,179 @@
         <v>16</v>
       </c>
       <c r="F9" s="6" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A10" s="11"/>
       <c r="B10" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="C10" s="23" t="s">
+      <c r="C10" s="24" t="s">
         <v>15</v>
       </c>
-      <c r="D10" s="24"/>
+      <c r="D10" s="25"/>
       <c r="E10" s="1" t="s">
         <v>18</v>
       </c>
       <c r="F10" s="6" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" s="11"/>
       <c r="B11" s="11"/>
-      <c r="C11" s="15" t="s">
+      <c r="C11" s="16" t="s">
         <v>17</v>
       </c>
-      <c r="D11" s="16"/>
+      <c r="D11" s="17"/>
       <c r="E11" s="1" t="s">
         <v>19</v>
       </c>
       <c r="F11" s="6" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" s="11"/>
-      <c r="B12" s="12"/>
-      <c r="C12" s="15" t="s">
-        <v>63</v>
-      </c>
-      <c r="D12" s="16"/>
+      <c r="B12" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="C12" s="26" t="s">
+        <v>31</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>54</v>
+      </c>
       <c r="E12" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="F12" s="6" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F12" s="42" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13" s="11"/>
-      <c r="B13" s="11" t="s">
-        <v>20</v>
-      </c>
-      <c r="C13" s="25" t="s">
-        <v>31</v>
-      </c>
+      <c r="B13" s="11"/>
+      <c r="C13" s="27"/>
       <c r="D13" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E13" s="1" t="s">
         <v>22</v>
       </c>
       <c r="F13" s="6" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14" s="11"/>
       <c r="B14" s="11"/>
-      <c r="C14" s="26"/>
+      <c r="C14" s="27"/>
       <c r="D14" s="1" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="E14" s="1" t="s">
         <v>23</v>
       </c>
       <c r="F14" s="6" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A15" s="11"/>
-      <c r="B15" s="11"/>
-      <c r="C15" s="26"/>
+      <c r="B15" s="12"/>
+      <c r="C15" s="28"/>
       <c r="D15" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E15" s="1" t="s">
         <v>24</v>
       </c>
       <c r="F15" s="6" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A16" s="11"/>
-      <c r="B16" s="12"/>
-      <c r="C16" s="27"/>
-      <c r="D16" s="1" t="s">
-        <v>56</v>
-      </c>
+      <c r="B16" s="29" t="s">
+        <v>26</v>
+      </c>
+      <c r="C16" s="30"/>
+      <c r="D16" s="31"/>
       <c r="E16" s="1" t="s">
         <v>25</v>
       </c>
       <c r="F16" s="6" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A17" s="11"/>
-      <c r="B17" s="13" t="s">
+      <c r="B17" s="32" t="s">
         <v>38</v>
       </c>
-      <c r="C17" s="15" t="s">
+      <c r="C17" s="16" t="s">
         <v>39</v>
       </c>
-      <c r="D17" s="16"/>
+      <c r="D17" s="17"/>
       <c r="E17" s="1" t="s">
         <v>27</v>
       </c>
       <c r="F17" s="6" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A18" s="12"/>
-      <c r="B18" s="14"/>
-      <c r="C18" s="15" t="s">
+      <c r="B18" s="33"/>
+      <c r="C18" s="16" t="s">
         <v>40</v>
       </c>
-      <c r="D18" s="16"/>
+      <c r="D18" s="17"/>
       <c r="E18" s="1" t="s">
         <v>28</v>
       </c>
       <c r="F18" s="6" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A19" s="10" t="s">
-        <v>65</v>
-      </c>
-      <c r="B19" s="18" t="s">
+        <v>64</v>
+      </c>
+      <c r="B19" s="13" t="s">
         <v>0</v>
       </c>
-      <c r="C19" s="19"/>
-      <c r="D19" s="20"/>
+      <c r="C19" s="14"/>
+      <c r="D19" s="15"/>
       <c r="E19" s="1" t="s">
         <v>32</v>
       </c>
       <c r="F19" s="6" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A20" s="11"/>
       <c r="B20" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="C20" s="15" t="s">
+      <c r="C20" s="16" t="s">
         <v>3</v>
       </c>
-      <c r="D20" s="16"/>
+      <c r="D20" s="17"/>
       <c r="E20" s="1" t="s">
         <v>33</v>
       </c>
       <c r="F20" s="6" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A21" s="11"/>
       <c r="B21" s="11"/>
-      <c r="C21" s="31" t="s">
+      <c r="C21" s="18" t="s">
         <v>5</v>
       </c>
       <c r="D21" s="2" t="s">
@@ -2172,13 +2169,13 @@
         <v>34</v>
       </c>
       <c r="F21" s="6" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A22" s="11"/>
       <c r="B22" s="11"/>
-      <c r="C22" s="32"/>
+      <c r="C22" s="19"/>
       <c r="D22" s="2" t="s">
         <v>59</v>
       </c>
@@ -2186,13 +2183,13 @@
         <v>35</v>
       </c>
       <c r="F22" s="6" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A23" s="11"/>
       <c r="B23" s="11"/>
-      <c r="C23" s="33"/>
+      <c r="C23" s="20"/>
       <c r="D23" s="3" t="s">
         <v>60</v>
       </c>
@@ -2200,10 +2197,10 @@
         <v>36</v>
       </c>
       <c r="F23" s="6" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A24" s="11"/>
       <c r="B24" s="11"/>
       <c r="C24" s="21" t="s">
@@ -2216,10 +2213,10 @@
         <v>37</v>
       </c>
       <c r="F24" s="6" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A25" s="11"/>
       <c r="B25" s="11"/>
       <c r="C25" s="22"/>
@@ -2230,10 +2227,10 @@
         <v>41</v>
       </c>
       <c r="F25" s="6" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A26" s="11"/>
       <c r="B26" s="11"/>
       <c r="C26" s="21" t="s">
@@ -2246,10 +2243,10 @@
         <v>42</v>
       </c>
       <c r="F26" s="6" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A27" s="11"/>
       <c r="B27" s="12"/>
       <c r="C27" s="22"/>
@@ -2260,45 +2257,45 @@
         <v>43</v>
       </c>
       <c r="F27" s="6" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A28" s="11"/>
-      <c r="B28" s="17" t="s">
+      <c r="B28" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="C28" s="23" t="s">
+      <c r="C28" s="24" t="s">
         <v>15</v>
       </c>
-      <c r="D28" s="24"/>
+      <c r="D28" s="25"/>
       <c r="E28" s="1" t="s">
         <v>44</v>
       </c>
       <c r="F28" s="6" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A29" s="11"/>
-      <c r="B29" s="17"/>
-      <c r="C29" s="15" t="s">
+      <c r="B29" s="23"/>
+      <c r="C29" s="16" t="s">
         <v>17</v>
       </c>
-      <c r="D29" s="16"/>
+      <c r="D29" s="17"/>
       <c r="E29" s="1" t="s">
         <v>45</v>
       </c>
       <c r="F29" s="6" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A30" s="11"/>
       <c r="B30" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="C30" s="25" t="s">
+      <c r="C30" s="26" t="s">
         <v>31</v>
       </c>
       <c r="D30" s="1" t="s">
@@ -2308,13 +2305,13 @@
         <v>46</v>
       </c>
       <c r="F30" s="6" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A31" s="11"/>
       <c r="B31" s="11"/>
-      <c r="C31" s="26"/>
+      <c r="C31" s="27"/>
       <c r="D31" s="1" t="s">
         <v>53</v>
       </c>
@@ -2322,13 +2319,13 @@
         <v>47</v>
       </c>
       <c r="F31" s="6" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A32" s="11"/>
       <c r="B32" s="11"/>
-      <c r="C32" s="26"/>
+      <c r="C32" s="27"/>
       <c r="D32" s="1" t="s">
         <v>55</v>
       </c>
@@ -2336,13 +2333,13 @@
         <v>48</v>
       </c>
       <c r="F32" s="6" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A33" s="11"/>
       <c r="B33" s="12"/>
-      <c r="C33" s="27"/>
+      <c r="C33" s="28"/>
       <c r="D33" s="1" t="s">
         <v>56</v>
       </c>
@@ -2350,55 +2347,71 @@
         <v>49</v>
       </c>
       <c r="F33" s="6" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A34" s="11"/>
-      <c r="B34" s="28" t="s">
+      <c r="B34" s="29" t="s">
         <v>26</v>
       </c>
-      <c r="C34" s="29"/>
-      <c r="D34" s="30"/>
+      <c r="C34" s="30"/>
+      <c r="D34" s="31"/>
       <c r="E34" s="1" t="s">
         <v>50</v>
       </c>
       <c r="F34" s="6" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A35" s="11"/>
-      <c r="B35" s="13" t="s">
+      <c r="B35" s="32" t="s">
         <v>38</v>
       </c>
-      <c r="C35" s="15" t="s">
+      <c r="C35" s="16" t="s">
         <v>39</v>
       </c>
-      <c r="D35" s="16"/>
+      <c r="D35" s="17"/>
       <c r="E35" s="1" t="s">
         <v>51</v>
       </c>
       <c r="F35" s="6" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A36" s="12"/>
-      <c r="B36" s="14"/>
-      <c r="C36" s="15" t="s">
+      <c r="B36" s="33"/>
+      <c r="C36" s="16" t="s">
         <v>40</v>
       </c>
-      <c r="D36" s="16"/>
+      <c r="D36" s="17"/>
       <c r="E36" s="1" t="s">
         <v>52</v>
       </c>
       <c r="F36" s="6" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="32">
+    <mergeCell ref="B16:D16"/>
+    <mergeCell ref="A1:A18"/>
+    <mergeCell ref="B1:D1"/>
+    <mergeCell ref="B2:B9"/>
+    <mergeCell ref="C2:D2"/>
+    <mergeCell ref="C3:C5"/>
+    <mergeCell ref="C6:C7"/>
+    <mergeCell ref="C8:C9"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="B10:B11"/>
+    <mergeCell ref="C10:D10"/>
+    <mergeCell ref="B12:B15"/>
+    <mergeCell ref="C12:C15"/>
+    <mergeCell ref="B17:B18"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="C18:D18"/>
     <mergeCell ref="A19:A36"/>
     <mergeCell ref="B19:D19"/>
     <mergeCell ref="B20:B27"/>
@@ -2415,22 +2428,6 @@
     <mergeCell ref="B35:B36"/>
     <mergeCell ref="C35:D35"/>
     <mergeCell ref="C36:D36"/>
-    <mergeCell ref="A1:A18"/>
-    <mergeCell ref="B1:D1"/>
-    <mergeCell ref="B2:B9"/>
-    <mergeCell ref="C2:D2"/>
-    <mergeCell ref="C3:C5"/>
-    <mergeCell ref="C6:C7"/>
-    <mergeCell ref="C8:C9"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="C12:D12"/>
-    <mergeCell ref="B10:B12"/>
-    <mergeCell ref="C10:D10"/>
-    <mergeCell ref="B13:B16"/>
-    <mergeCell ref="C13:C16"/>
-    <mergeCell ref="B17:B18"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="C18:D18"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2438,9 +2435,9 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{77248F5E-948B-441A-9D1F-3CCED07E79FC}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:F26"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="39.140625" customWidth="1"/>
     <col min="2" max="2" width="12.28515625" bestFit="1" customWidth="1"/>
@@ -2450,42 +2447,42 @@
     <col min="6" max="6" width="19.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" s="10" t="s">
         <v>61</v>
       </c>
-      <c r="B1" s="28" t="s">
+      <c r="B1" s="29" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="29"/>
-      <c r="D1" s="30"/>
+      <c r="C1" s="30"/>
+      <c r="D1" s="31"/>
       <c r="E1" s="1" t="s">
         <v>1</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" s="11"/>
       <c r="B2" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="C2" s="34" t="s">
+      <c r="C2" s="36" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="35"/>
+      <c r="D2" s="37"/>
       <c r="E2" s="1" t="s">
         <v>2</v>
       </c>
       <c r="F2" s="8" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" s="11"/>
       <c r="B3" s="11"/>
-      <c r="C3" s="36" t="s">
+      <c r="C3" s="34" t="s">
         <v>31</v>
       </c>
       <c r="D3" s="4" t="s">
@@ -2495,13 +2492,13 @@
         <v>4</v>
       </c>
       <c r="F3" s="8" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" s="11"/>
       <c r="B4" s="12"/>
-      <c r="C4" s="37"/>
+      <c r="C4" s="35"/>
       <c r="D4" s="4" t="s">
         <v>10</v>
       </c>
@@ -2509,45 +2506,45 @@
         <v>6</v>
       </c>
       <c r="F4" s="8" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" s="11"/>
       <c r="B5" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="C5" s="38" t="s">
+      <c r="C5" s="39" t="s">
         <v>15</v>
       </c>
-      <c r="D5" s="39"/>
+      <c r="D5" s="40"/>
       <c r="E5" s="1" t="s">
         <v>9</v>
       </c>
       <c r="F5" s="8" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" s="11"/>
       <c r="B6" s="11"/>
-      <c r="C6" s="34" t="s">
+      <c r="C6" s="36" t="s">
         <v>17</v>
       </c>
-      <c r="D6" s="35"/>
+      <c r="D6" s="37"/>
       <c r="E6" s="1" t="s">
         <v>11</v>
       </c>
       <c r="F6" s="8" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" s="11"/>
       <c r="B7" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="C7" s="36" t="s">
+      <c r="C7" s="34" t="s">
         <v>31</v>
       </c>
       <c r="D7" s="4" t="s">
@@ -2557,13 +2554,13 @@
         <v>12</v>
       </c>
       <c r="F7" s="8" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" s="11"/>
       <c r="B8" s="11"/>
-      <c r="C8" s="40"/>
+      <c r="C8" s="38"/>
       <c r="D8" s="4" t="s">
         <v>53</v>
       </c>
@@ -2571,13 +2568,13 @@
         <v>13</v>
       </c>
       <c r="F8" s="8" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9" s="11"/>
       <c r="B9" s="11"/>
-      <c r="C9" s="40"/>
+      <c r="C9" s="38"/>
       <c r="D9" s="4" t="s">
         <v>55</v>
       </c>
@@ -2585,13 +2582,13 @@
         <v>16</v>
       </c>
       <c r="F9" s="8" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" s="11"/>
       <c r="B10" s="12"/>
-      <c r="C10" s="37"/>
+      <c r="C10" s="35"/>
       <c r="D10" s="4" t="s">
         <v>56</v>
       </c>
@@ -2599,89 +2596,89 @@
         <v>18</v>
       </c>
       <c r="F10" s="8" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" s="11"/>
-      <c r="B11" s="28" t="s">
+      <c r="B11" s="29" t="s">
         <v>26</v>
       </c>
-      <c r="C11" s="29"/>
-      <c r="D11" s="30"/>
+      <c r="C11" s="30"/>
+      <c r="D11" s="31"/>
       <c r="E11" s="1" t="s">
         <v>19</v>
       </c>
       <c r="F11" s="8" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" s="11"/>
-      <c r="B12" s="36" t="s">
+      <c r="B12" s="34" t="s">
         <v>38</v>
       </c>
-      <c r="C12" s="34" t="s">
+      <c r="C12" s="36" t="s">
         <v>39</v>
       </c>
-      <c r="D12" s="35"/>
+      <c r="D12" s="37"/>
       <c r="E12" s="1" t="s">
         <v>21</v>
       </c>
       <c r="F12" s="8" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13" s="12"/>
-      <c r="B13" s="37"/>
-      <c r="C13" s="34" t="s">
+      <c r="B13" s="35"/>
+      <c r="C13" s="36" t="s">
         <v>40</v>
       </c>
-      <c r="D13" s="35"/>
+      <c r="D13" s="37"/>
       <c r="E13" s="1" t="s">
         <v>22</v>
       </c>
       <c r="F13" s="8" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14" s="10" t="s">
         <v>62</v>
       </c>
-      <c r="B14" s="28" t="s">
+      <c r="B14" s="29" t="s">
         <v>0</v>
       </c>
-      <c r="C14" s="29"/>
-      <c r="D14" s="30"/>
+      <c r="C14" s="30"/>
+      <c r="D14" s="31"/>
       <c r="E14" s="1" t="s">
         <v>23</v>
       </c>
       <c r="F14" s="8" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A15" s="11"/>
       <c r="B15" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="C15" s="34" t="s">
+      <c r="C15" s="36" t="s">
         <v>3</v>
       </c>
-      <c r="D15" s="35"/>
+      <c r="D15" s="37"/>
       <c r="E15" s="1" t="s">
         <v>24</v>
       </c>
       <c r="F15" s="8" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A16" s="11"/>
       <c r="B16" s="11"/>
-      <c r="C16" s="36" t="s">
+      <c r="C16" s="34" t="s">
         <v>31</v>
       </c>
       <c r="D16" s="4" t="s">
@@ -2691,13 +2688,13 @@
         <v>25</v>
       </c>
       <c r="F16" s="8" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A17" s="11"/>
       <c r="B17" s="12"/>
-      <c r="C17" s="37"/>
+      <c r="C17" s="35"/>
       <c r="D17" s="4" t="s">
         <v>10</v>
       </c>
@@ -2705,45 +2702,45 @@
         <v>27</v>
       </c>
       <c r="F17" s="8" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A18" s="11"/>
       <c r="B18" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="C18" s="38" t="s">
+      <c r="C18" s="39" t="s">
         <v>15</v>
       </c>
-      <c r="D18" s="39"/>
+      <c r="D18" s="40"/>
       <c r="E18" s="1" t="s">
         <v>28</v>
       </c>
       <c r="F18" s="8" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A19" s="11"/>
       <c r="B19" s="11"/>
-      <c r="C19" s="34" t="s">
+      <c r="C19" s="36" t="s">
         <v>17</v>
       </c>
-      <c r="D19" s="35"/>
+      <c r="D19" s="37"/>
       <c r="E19" s="1" t="s">
         <v>32</v>
       </c>
       <c r="F19" s="8" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A20" s="11"/>
       <c r="B20" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="C20" s="36" t="s">
+      <c r="C20" s="34" t="s">
         <v>31</v>
       </c>
       <c r="D20" s="4" t="s">
@@ -2753,13 +2750,13 @@
         <v>33</v>
       </c>
       <c r="F20" s="8" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A21" s="11"/>
       <c r="B21" s="11"/>
-      <c r="C21" s="40"/>
+      <c r="C21" s="38"/>
       <c r="D21" s="4" t="s">
         <v>53</v>
       </c>
@@ -2767,13 +2764,13 @@
         <v>34</v>
       </c>
       <c r="F21" s="8" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A22" s="11"/>
       <c r="B22" s="11"/>
-      <c r="C22" s="40"/>
+      <c r="C22" s="38"/>
       <c r="D22" s="4" t="s">
         <v>55</v>
       </c>
@@ -2781,13 +2778,13 @@
         <v>35</v>
       </c>
       <c r="F22" s="8" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A23" s="11"/>
       <c r="B23" s="12"/>
-      <c r="C23" s="37"/>
+      <c r="C23" s="35"/>
       <c r="D23" s="4" t="s">
         <v>56</v>
       </c>
@@ -2795,55 +2792,67 @@
         <v>36</v>
       </c>
       <c r="F23" s="8" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A24" s="11"/>
-      <c r="B24" s="28" t="s">
+      <c r="B24" s="29" t="s">
         <v>26</v>
       </c>
-      <c r="C24" s="29"/>
-      <c r="D24" s="30"/>
+      <c r="C24" s="30"/>
+      <c r="D24" s="31"/>
       <c r="E24" s="1" t="s">
         <v>37</v>
       </c>
       <c r="F24" s="8" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A25" s="11"/>
-      <c r="B25" s="36" t="s">
+      <c r="B25" s="34" t="s">
         <v>38</v>
       </c>
-      <c r="C25" s="34" t="s">
+      <c r="C25" s="36" t="s">
         <v>39</v>
       </c>
-      <c r="D25" s="35"/>
+      <c r="D25" s="37"/>
       <c r="E25" s="1" t="s">
         <v>41</v>
       </c>
       <c r="F25" s="8" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A26" s="12"/>
-      <c r="B26" s="37"/>
-      <c r="C26" s="34" t="s">
+      <c r="B26" s="35"/>
+      <c r="C26" s="36" t="s">
         <v>40</v>
       </c>
-      <c r="D26" s="35"/>
+      <c r="D26" s="37"/>
       <c r="E26" s="1" t="s">
         <v>42</v>
       </c>
       <c r="F26" s="8" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="28">
+    <mergeCell ref="C26:D26"/>
+    <mergeCell ref="B1:D1"/>
+    <mergeCell ref="C3:C4"/>
+    <mergeCell ref="C2:D2"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="B5:B6"/>
+    <mergeCell ref="B2:B4"/>
+    <mergeCell ref="C6:D6"/>
+    <mergeCell ref="C5:D5"/>
+    <mergeCell ref="B7:B10"/>
+    <mergeCell ref="C7:C10"/>
+    <mergeCell ref="B11:D11"/>
     <mergeCell ref="A1:A13"/>
     <mergeCell ref="B12:B13"/>
     <mergeCell ref="C12:D12"/>
@@ -2860,18 +2869,6 @@
     <mergeCell ref="B24:D24"/>
     <mergeCell ref="B25:B26"/>
     <mergeCell ref="C25:D25"/>
-    <mergeCell ref="C26:D26"/>
-    <mergeCell ref="B1:D1"/>
-    <mergeCell ref="C3:C4"/>
-    <mergeCell ref="C2:D2"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="B5:B6"/>
-    <mergeCell ref="B2:B4"/>
-    <mergeCell ref="C6:D6"/>
-    <mergeCell ref="C5:D5"/>
-    <mergeCell ref="B7:B10"/>
-    <mergeCell ref="C7:C10"/>
-    <mergeCell ref="B11:D11"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2879,9 +2876,9 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AD255B99-430C-4189-8DC3-75426731E486}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:D18"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="22.7109375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="27.28515625" bestFit="1" customWidth="1"/>
@@ -2889,219 +2886,219 @@
     <col min="4" max="4" width="20.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" s="21" t="s">
+        <v>65</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>66</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>67</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D1" s="9" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" s="41"/>
       <c r="B2" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" s="41"/>
       <c r="B3" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D3" s="9" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" s="41"/>
       <c r="B4" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D4" s="9" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" s="41"/>
       <c r="B5" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D5" s="9" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" s="22"/>
       <c r="B6" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D6" s="9" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" s="21" t="s">
+        <v>72</v>
+      </c>
+      <c r="B7" s="1" t="s">
         <v>73</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>74</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D7" s="9" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" s="41"/>
       <c r="B8" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D8" s="9" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" s="41"/>
       <c r="B9" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D9" s="9" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" s="41"/>
       <c r="B10" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D10" s="9" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" s="22"/>
       <c r="B11" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D11" s="9" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12" s="21" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D12" s="9" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13" s="41"/>
       <c r="B13" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D13" s="9" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A14" s="41"/>
       <c r="B14" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>23</v>
       </c>
       <c r="D14" s="9" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A15" s="41"/>
       <c r="B15" s="1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>24</v>
       </c>
       <c r="D15" s="9" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A16" s="22"/>
       <c r="B16" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>25</v>
       </c>
       <c r="D16" s="9" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17" s="21" t="s">
+        <v>81</v>
+      </c>
+      <c r="B17" s="1" t="s">
         <v>82</v>
-      </c>
-      <c r="B17" s="1" t="s">
-        <v>83</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D17" s="9" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A18" s="22"/>
       <c r="B18" s="1" t="s">
         <v>26</v>
@@ -3110,7 +3107,7 @@
         <v>28</v>
       </c>
       <c r="D18" s="9" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
   </sheetData>
